--- a/experiments/prompt-tuning/hc+ft/Results/FLICKR_QWEN/Flickr_prompt05.xlsx
+++ b/experiments/prompt-tuning/hc+ft/Results/FLICKR_QWEN/Flickr_prompt05.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UshariRanasinghe\Desktop\Projects\vlm-research\experiments\prompt-tuning\hc+ft\Results\FLICKR_QWEN\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEC573B-740C-41E6-BA89-BC80B628C27D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -149,8 +155,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +219,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -233,7 +247,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -271,7 +291,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -309,7 +335,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -347,7 +379,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -385,7 +423,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -423,7 +467,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -461,7 +511,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -499,7 +555,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -537,7 +599,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -575,7 +643,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -644,7 +718,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -676,9 +750,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -710,6 +802,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -885,11 +995,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:J12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="126.453125" customWidth="1"/>
+    <col min="5" max="5" width="167.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -918,7 +1032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>0</v>
       </c>
@@ -932,10 +1046,10 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>0.4935004353523255</v>
+        <v>0.49350043535232552</v>
       </c>
       <c r="G2">
-        <v>0.1290322580645162</v>
+        <v>0.12903225806451621</v>
       </c>
       <c r="H2">
         <v>1.363244634388977</v>
@@ -947,7 +1061,7 @@
         <v>18.79121112823486</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -961,13 +1075,13 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.2920052409172058</v>
+        <v>0.29200524091720581</v>
       </c>
       <c r="G3">
         <v>0.2</v>
       </c>
       <c r="H3">
-        <v>1.73232476221268</v>
+        <v>1.7323247622126801</v>
       </c>
       <c r="I3">
         <v>6945.15576171875</v>
@@ -976,7 +1090,7 @@
         <v>1.77082347869873</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -990,22 +1104,22 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.6172617912292481</v>
+        <v>0.61726179122924807</v>
       </c>
       <c r="G4">
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="H4">
-        <v>0.702383930687029</v>
+        <v>0.70238393068702898</v>
       </c>
       <c r="I4">
         <v>6945.15576171875</v>
       </c>
       <c r="J4">
-        <v>1.14096212387085</v>
+        <v>1.1409621238708501</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1022,7 +1136,7 @@
         <v>0.6306077241897583</v>
       </c>
       <c r="G5">
-        <v>0.08333333333333333</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="H5">
         <v>1.502331444744673</v>
@@ -1034,7 +1148,7 @@
         <v>1.547854900360107</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1051,10 +1165,10 @@
         <v>0.6739171504974365</v>
       </c>
       <c r="G6">
-        <v>0.4444444444444445</v>
+        <v>0.44444444444444448</v>
       </c>
       <c r="H6">
-        <v>1.674486314072423</v>
+        <v>1.6744863140724231</v>
       </c>
       <c r="I6">
         <v>6945.15576171875</v>
@@ -1063,7 +1177,7 @@
         <v>1.037651062011719</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1077,22 +1191,22 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0.4986760497093201</v>
+        <v>0.49867604970932011</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.7843595238565919</v>
+        <v>0.78435952385659191</v>
       </c>
       <c r="I7">
         <v>6945.15576171875</v>
       </c>
       <c r="J7">
-        <v>1.284139633178711</v>
+        <v>1.2841396331787109</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1106,10 +1220,10 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>0.6114264726638794</v>
+        <v>0.61142647266387939</v>
       </c>
       <c r="G8">
-        <v>0.2222222222222222</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="H8">
         <v>1.722046577706416</v>
@@ -1118,10 +1232,10 @@
         <v>6945.15576171875</v>
       </c>
       <c r="J8">
-        <v>1.208746433258057</v>
+        <v>1.2087464332580571</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1135,22 +1249,22 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>0.5260249614715576</v>
+        <v>0.52602496147155764</v>
       </c>
       <c r="G9">
-        <v>0.4347826086956522</v>
+        <v>0.43478260869565222</v>
       </c>
       <c r="H9">
-        <v>2.045684420203935</v>
+        <v>2.0456844202039348</v>
       </c>
       <c r="I9">
         <v>6949.91796875</v>
       </c>
       <c r="J9">
-        <v>1.409712791442871</v>
+        <v>1.4097127914428711</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1164,13 +1278,13 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0.350447291135788</v>
+        <v>0.35044729113578799</v>
       </c>
       <c r="G10">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="H10">
-        <v>0.865361477833295</v>
+        <v>0.86536147783329498</v>
       </c>
       <c r="I10">
         <v>6946.14501953125</v>
@@ -1179,7 +1293,7 @@
         <v>1.279898881912231</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1193,10 +1307,10 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.5684092402458191</v>
+        <v>0.56840924024581907</v>
       </c>
       <c r="G11">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="H11">
         <v>3.645108419171355</v>
@@ -1205,7 +1319,29 @@
         <v>6942.2744140625</v>
       </c>
       <c r="J11">
-        <v>0.7714865207672119</v>
+        <v>0.77148652076721191</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <f>AVERAGE(F3:F11)</f>
+        <v>0.52986399134000139</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:J12" si="0">AVERAGE(G3:G11)</f>
+        <v>0.21899219942698206</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>1.6304540967209331</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>6945.0446506076387</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>1.2723639806111653</v>
       </c>
     </row>
   </sheetData>
